--- a/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>EDR</t>
   </si>
@@ -656,264 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1582700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1344400</v>
       </c>
-      <c r="E8" s="3">
-        <v>1436200</v>
-      </c>
       <c r="F8" s="3">
+        <v>3033000</v>
+      </c>
+      <c r="G8" s="3">
         <v>1596800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1260400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1221400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1312500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1473800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1505600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1391300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1111300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1069600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4571000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1038800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1009700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1213700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>898900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>780700</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>645400</v>
+      </c>
+      <c r="E9" s="3">
         <v>487900</v>
       </c>
-      <c r="E9" s="3">
-        <v>584000</v>
-      </c>
       <c r="F9" s="3">
+        <v>1308300</v>
+      </c>
+      <c r="G9" s="3">
         <v>724300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>464200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>398500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>508400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>694600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>806600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>673200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>571000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>546400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2323300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>513500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>572400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1722100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>937300</v>
+      </c>
+      <c r="E10" s="3">
         <v>856500</v>
       </c>
-      <c r="E10" s="3">
-        <v>852200</v>
-      </c>
       <c r="F10" s="3">
+        <v>1724700</v>
+      </c>
+      <c r="G10" s="3">
         <v>872500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>796200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>822900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>804100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>779200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>699000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>718100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>540300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>523200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2247700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>525300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>437300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-508400</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>445600</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,50 +1062,53 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-690300</v>
+      </c>
+      <c r="E14" s="3">
         <v>28200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-23300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-463600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>32400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>2500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1102,64 +1121,70 @@
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>152500</v>
+      </c>
+      <c r="E15" s="3">
         <v>81200</v>
       </c>
-      <c r="E15" s="3">
-        <v>61100</v>
-      </c>
       <c r="F15" s="3">
+        <v>127800</v>
+      </c>
+      <c r="G15" s="3">
         <v>66800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>71600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>63600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>65600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>66000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>74800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>71700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>69200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>67200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>280700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>64800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>78500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>366000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>853100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1312500</v>
       </c>
-      <c r="E17" s="3">
-        <v>1277800</v>
-      </c>
       <c r="F17" s="3">
+        <v>2738000</v>
+      </c>
+      <c r="G17" s="3">
         <v>1460200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1142300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1064200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1161500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>836200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1452100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1254000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1447400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>975100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4360400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1005900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1032300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3720900</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>729600</v>
+      </c>
+      <c r="E18" s="3">
         <v>31900</v>
       </c>
-      <c r="E18" s="3">
-        <v>158400</v>
-      </c>
       <c r="F18" s="3">
+        <v>295000</v>
+      </c>
+      <c r="G18" s="3">
         <v>136600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>118100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>157200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>151000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>637600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>137300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-336100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>94500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>210600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2507200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>-62800</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,288 +1343,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-658000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-33200</v>
       </c>
-      <c r="E20" s="3">
-        <v>751800</v>
-      </c>
       <c r="F20" s="3">
+        <v>778700</v>
+      </c>
+      <c r="G20" s="3">
         <v>26800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-822900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-57200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-94500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-69300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-61700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2457300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>224100</v>
+      </c>
+      <c r="E21" s="3">
         <v>79900</v>
       </c>
-      <c r="E21" s="3">
-        <v>971400</v>
-      </c>
       <c r="F21" s="3">
+        <v>1201500</v>
+      </c>
+      <c r="G21" s="3">
         <v>230100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-633100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>219700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>212900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>646400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>33800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>201200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-259000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>158500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>422100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>117100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5700</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E22" s="3">
         <v>82000</v>
       </c>
-      <c r="E22" s="3">
-        <v>90300</v>
-      </c>
       <c r="F22" s="3">
+        <v>175400</v>
+      </c>
+      <c r="G22" s="3">
         <v>85100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>84900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>75600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>62500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>59300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>60700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>55800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>83800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>68400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>270900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>70700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>71400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>277200</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-83200</v>
       </c>
-      <c r="E23" s="3">
-        <v>820000</v>
-      </c>
       <c r="F23" s="3">
+        <v>898200</v>
+      </c>
+      <c r="G23" s="3">
         <v>78300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-789600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>80500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>84800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>521100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-101700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>73800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-412000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-129600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-155600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-327100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>-151500</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E24" s="3">
         <v>30000</v>
       </c>
-      <c r="E24" s="3">
-        <v>140400</v>
-      </c>
       <c r="F24" s="3">
+        <v>175900</v>
+      </c>
+      <c r="G24" s="3">
         <v>35500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-642500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-17200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-80600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-22400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>88200</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>87900</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-113200</v>
       </c>
-      <c r="E26" s="3">
-        <v>679500</v>
-      </c>
       <c r="F26" s="3">
+        <v>722300</v>
+      </c>
+      <c r="G26" s="3">
         <v>42800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-147100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>72000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>538300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-473000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-133000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-32100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-133200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-415300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>-239400</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-69200</v>
       </c>
-      <c r="E27" s="3">
-        <v>403200</v>
-      </c>
       <c r="F27" s="3">
-        <v>8000</v>
+        <v>408800</v>
       </c>
       <c r="G27" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-206200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>319500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-319600</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-548800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-134700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-378500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>-243800</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1853,26 +1913,29 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>-5000</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3">
         <v>-5000</v>
       </c>
       <c r="Q29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>695000</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>-50200</v>
       </c>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>658000</v>
+      </c>
+      <c r="E32" s="3">
         <v>33200</v>
       </c>
-      <c r="E32" s="3">
-        <v>-751800</v>
-      </c>
       <c r="F32" s="3">
+        <v>-778700</v>
+      </c>
+      <c r="G32" s="3">
         <v>-26800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>822900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>57200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>94500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>69300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>61700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2457300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-69200</v>
       </c>
-      <c r="E33" s="3">
-        <v>403200</v>
-      </c>
       <c r="F33" s="3">
-        <v>8000</v>
+        <v>408800</v>
       </c>
       <c r="G33" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-206200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>319500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-319600</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-553800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-57900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-134700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>316500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-69200</v>
       </c>
-      <c r="E35" s="3">
-        <v>403200</v>
-      </c>
       <c r="F35" s="3">
-        <v>8000</v>
+        <v>408800</v>
       </c>
       <c r="G35" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-206200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>319500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-319600</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-553800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-57900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-134700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>316500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1166500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1337700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1616500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>718700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>767800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>970800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1824000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2030300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1561000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1028700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>869800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>880900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>705300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>830900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>499700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,64 +2513,70 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>939800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1083100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>982200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>991600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>917000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>893400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>826700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>760500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>615000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>639400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>597600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>519500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>779500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>806900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>789600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2536,288 +2631,306 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1358200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1266300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1009500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>827900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>851900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>823000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>810300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>625400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1577700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1642000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>619300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>551400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>536900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>518500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>511000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3464500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3687100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3608100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2538200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2536700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2687100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3461000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3416200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3753700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3310100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2086700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1951700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2021800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2156300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1800400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>398000</v>
+      </c>
+      <c r="E47" s="3">
         <v>387000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>344000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>348500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>337000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>407400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>483600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>492700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>298200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>285800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>295000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>225100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>580100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>920200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1178900</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1265300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1221800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>801500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1049000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1042900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>967200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>987700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>991500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1003500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>961500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>963500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>979400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1025200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1002500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>973800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15364200</v>
+      </c>
+      <c r="E49" s="3">
         <v>15461700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7258300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7492100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7490300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7437600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6456600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6132200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6118200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5970000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5992000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5731800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5494500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5572700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5637700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1052700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1144000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1304600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1191800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1097000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>416500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>347800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>326700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>260900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>203400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>966900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>719800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>170800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>351900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>294600</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21544800</v>
+      </c>
+      <c r="E54" s="3">
         <v>21901600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13316600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12619700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12503800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11915900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11736600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11359400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11434500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10730900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10304100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9607700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9292300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10003600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9885300</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,344 +3269,363 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>587600</v>
+      </c>
+      <c r="E57" s="3">
         <v>590100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>673700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>615200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>540100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>527400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>558900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>556200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>522100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>497200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>509500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>451700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>460500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E58" s="3">
         <v>63000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>99000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>88700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>89000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>87100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>82600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>82000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>75900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>94800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>103200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>115400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>107700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>93300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2150400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2269700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1860700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1839100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1725600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1719600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1581600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1388700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2064600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2075100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1548500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1317100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1188200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1466000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1280400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2796900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2922800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2633400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2543000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2414500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2348800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2268700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1998800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2705400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2707100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2165500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1917500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1813100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2025400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1834200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4969400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4983400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5011400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5062500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5080200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5338400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5596700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5621400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5631700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5032500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5255700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5768300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4929900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4491600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4525200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2055900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2125700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1574600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1617200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1702500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>805200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>745900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>772700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>766000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>736500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>753500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>747600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>681200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>718500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>660200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16760100</v>
+      </c>
+      <c r="E66" s="3">
         <v>17138600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10812200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10594900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10623000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9925400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9835800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9689000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10187500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9523100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9165400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9312100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8335300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8613000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8385600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,44 +4116,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-117100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-52200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>195000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-208200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-216200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10000</v>
       </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
       <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3">
         <v>22900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-296600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-277100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-319600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
@@ -3996,14 +4169,17 @@
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4784700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4763100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2504300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2024800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1880800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1990500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1900800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1670300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1247000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1207700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1138700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>295600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>957000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1390600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1499800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-69200</v>
       </c>
-      <c r="E81" s="3">
-        <v>403200</v>
-      </c>
       <c r="F81" s="3">
-        <v>8000</v>
+        <v>408800</v>
       </c>
       <c r="G81" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-206200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>319500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-319600</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-553800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-57900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-134700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>316500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>152500</v>
+      </c>
+      <c r="E83" s="3">
         <v>81200</v>
       </c>
-      <c r="E83" s="3">
-        <v>61100</v>
-      </c>
       <c r="F83" s="3">
+        <v>127800</v>
+      </c>
+      <c r="G83" s="3">
         <v>66800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>71600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>63600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>65600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>66000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>74800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>71700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>69200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>280700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>78500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>105800</v>
+      </c>
+      <c r="E89" s="3">
         <v>94500</v>
       </c>
-      <c r="E89" s="3">
-        <v>96600</v>
-      </c>
       <c r="F89" s="3">
+        <v>197400</v>
+      </c>
+      <c r="G89" s="3">
         <v>100800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>96400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>189300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>271200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-29400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>176300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>250800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-51400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-70800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>392900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>315800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-59000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-53700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-39000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-34000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-135400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-38900</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-72900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58100</v>
       </c>
-      <c r="E94" s="3">
-        <v>935500</v>
-      </c>
       <c r="F94" s="3">
+        <v>861400</v>
+      </c>
+      <c r="G94" s="3">
         <v>-74100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-784200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-421600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>544700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-250500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-380200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>7600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>46100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>153300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-42500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,13 +5313,14 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-27100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -5096,11 +5329,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-10100</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -5108,37 +5341,40 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-5200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-121000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-37000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-244300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-326000</v>
       </c>
-      <c r="E100" s="3">
-        <v>-74000</v>
-      </c>
       <c r="F100" s="3">
+        <v>-163900</v>
+      </c>
+      <c r="G100" s="3">
         <v>-89900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-281700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-275400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>26300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-19100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>589100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-26400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>475300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-77800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-428100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-145100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6600</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>3500</v>
       </c>
       <c r="G101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H101" s="3">
         <v>9800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-203400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-296100</v>
       </c>
-      <c r="E102" s="3">
-        <v>958100</v>
-      </c>
       <c r="F102" s="3">
+        <v>898400</v>
+      </c>
+      <c r="G102" s="3">
         <v>-59700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-219000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-883900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-140700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>496600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>514300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>184600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>46000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-142200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>416100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-245300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>EDR</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1850300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1582700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1344400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3033000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1596800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1260400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1221400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1312500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1473800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1505600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1391300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1111300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1069600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4571000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1038800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1009700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1213700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>898900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>780700</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>844600</v>
+      </c>
+      <c r="E9" s="3">
         <v>645400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>487900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1308300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>724300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>464200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>398500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>508400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>694600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>806600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>673200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>571000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>546400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2323300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>513500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>572400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1722100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1005700</v>
+      </c>
+      <c r="E10" s="3">
         <v>937300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>856500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1724700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>872500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>796200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>822900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>804100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>779200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>699000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>718100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>540300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>523200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2247700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>525300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>437300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-508400</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>445600</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,53 +1082,56 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-690300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-23300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-463600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>32400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1124,67 +1144,73 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E15" s="3">
         <v>152500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>81200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>127800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>66800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>71600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>63600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>65600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>66000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>74800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>71700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>280700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>64800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>78500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>366000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2161400</v>
+      </c>
+      <c r="E17" s="3">
         <v>853100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1312500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2738000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1460200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1142300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1064200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1161500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>836200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1452100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1254000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1447400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>975100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4360400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1005900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1032300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3720900</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-311100</v>
+      </c>
+      <c r="E18" s="3">
         <v>729600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>31900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>295000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>136600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>118100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>157200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>151000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>637600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>53500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>137300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-336100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>94500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>210600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-22600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2507200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>-62800</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,303 +1377,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-658000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-33200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>778700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-822900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-57200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-94500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-69300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-61700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2457300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-160100</v>
+      </c>
+      <c r="E21" s="3">
         <v>224100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>79900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1201500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>230100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-633100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>219700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>212900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>646400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>33800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>201200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-259000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>158500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>422100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>117100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E22" s="3">
         <v>88300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>82000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>175400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>85100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>84900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>75600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>62500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>59300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>60700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>55800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>83800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>68400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>270900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>70700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>71400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>277200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-413000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-83200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>898200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>78300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-789600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>80500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>84800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>521100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-101700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>73800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-412000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-129600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-155600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-327100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>-151500</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-111800</v>
+      </c>
+      <c r="E24" s="3">
         <v>13900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>175900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>35500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-642500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-17200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-80600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>60900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-22400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>88200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>87900</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-301200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-113200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>722300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>42800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-147100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>72000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>82100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>538300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>81500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-473000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-133000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-32100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-133200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-415300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>-239400</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-137300</v>
+      </c>
+      <c r="E27" s="3">
         <v>17300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-69200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>408800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-206200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>319500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-319600</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-548800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-52900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-134700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-378500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>-243800</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,31 +1933,34 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1916,26 +1977,29 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
-        <v>-5000</v>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>-5000</v>
       </c>
       <c r="R29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>695000</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>-50200</v>
       </c>
     </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>658000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>33200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-778700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>822900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>57200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>94500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>69300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>61700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2457300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-137300</v>
+      </c>
+      <c r="E33" s="3">
         <v>17300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-69200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>408800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-206200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>319500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-319600</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-553800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-57900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-134700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>316500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-137300</v>
+      </c>
+      <c r="E35" s="3">
         <v>17300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-69200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>408800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-206200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>319500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-319600</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-553800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-57900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-134700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>316500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2484,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>778600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1166500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1337700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1616500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>718700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>767800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>970800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1824000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2030300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1561000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1028700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>869800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>880900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>705300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>830900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>499700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,67 +2606,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1087900</v>
+      </c>
+      <c r="E43" s="3">
         <v>939800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1083100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>982200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>991600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>917000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>893400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>826700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>760500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>615000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>639400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>597600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>519500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>779500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>806900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>789600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,303 +2730,321 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1536500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1358200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1266300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1009500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>827900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>851900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>823000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>810300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>625400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1577700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1642000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>619300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>551400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>536900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>518500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>511000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3403000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3464500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3687100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3608100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2538200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2536700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2687100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3461000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3416200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3753700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3310100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2086700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1951700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2021800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2156300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1800400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>404200</v>
+      </c>
+      <c r="E47" s="3">
         <v>398000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>387000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>344000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>348500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>337000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>407400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>483600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>492700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>298200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>285800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>295000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>225100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>580100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>920200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1178900</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1386000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1265300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1221800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>801500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1049000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1042900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>967200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>987700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>991500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1003500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>961500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>963500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>979400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1025200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1002500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>973800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15180900</v>
+      </c>
+      <c r="E49" s="3">
         <v>15364200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15461700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7258300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7492100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7490300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7437600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6456600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6132200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6118200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5970000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5992000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5731800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5494500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5572700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5637700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,67 +3164,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1138600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1052700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1144000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1304600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1191800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1097000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>416500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>347800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>326700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>260900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>203400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>966900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>719800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>170800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>351900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>294600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21512700</v>
+      </c>
+      <c r="E54" s="3">
         <v>21544800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21901600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13316600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12619700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12503800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11915900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11736600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11359400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11434500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10730900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10304100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9607700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9292300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10003600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9885300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,362 +3400,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>608900</v>
+      </c>
+      <c r="E57" s="3">
         <v>587600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>590100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>673700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>615200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>540100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>527400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>558900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>556200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>522100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>497200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>509500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>451700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>460500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E58" s="3">
         <v>58900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>63000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>99000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>88300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>89000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>87100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>82600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>82000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>75900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>94800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>103200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>115400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>107700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>93300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2264200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2150400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2269700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1860700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1839100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1725600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1719600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1581600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1388700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2064600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2075100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1548500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1317100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1188200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1466000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1280400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2927800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2796900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2922800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2633400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2543000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2414500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2348800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2268700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1998800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2705400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2707100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2165500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1917500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1813100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2025400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1834200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4955400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4969400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4983400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5011400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5062500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5080200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5338400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5596700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5621400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5631700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5032500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5255700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5768300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4929900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4491600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4525200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2215900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2055900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2125700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1574600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1617200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1702500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>805200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>745900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>772700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>766000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>736500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>753500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>747600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>681200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>718500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>660200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16850700</v>
+      </c>
+      <c r="E66" s="3">
         <v>16760100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17138600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10812200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10594900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10623000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9925400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9835800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9689000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10187500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9523100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9165400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9312100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8335300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8613000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8385600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,47 +4290,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-272500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-117100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>195000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-208200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-216200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10000</v>
       </c>
-      <c r="J72" s="3">
-        <v>0</v>
-      </c>
       <c r="K72" s="3">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3">
         <v>22900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-296600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-277100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-319600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4172,14 +4346,17 @@
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4662100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4784700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4763100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2504300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2024800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1880800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1990500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1900800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1670300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1247000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1207700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1138700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>295600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>957000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1390600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1499800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-137300</v>
+      </c>
+      <c r="E81" s="3">
         <v>17300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-69200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>408800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-206200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>319500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-319600</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-553800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-57900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-134700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>316500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,67 +4817,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E83" s="3">
         <v>152500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>127800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>66800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>71600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>63600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>65600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>66000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>74800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>71700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>69200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>67200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>280700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>64800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>78500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-136300</v>
+      </c>
+      <c r="E89" s="3">
         <v>105800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>94500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>197400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>96400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>189300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>271200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-29400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>176300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>250800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-51400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-70800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>392900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>315800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-59000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-72800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-53700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-56000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-53200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-34000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-58800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-135400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38900</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-72200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-58100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>861400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-74100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-784200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-421600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>544700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-250500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-380200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>7600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>46100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>153300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-42500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5323,7 +5557,7 @@
         <v>-27100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-27100</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -5332,11 +5566,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-10100</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -5344,37 +5578,40 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-5200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-12100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-37000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +5793,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-131500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-244300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-326000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-163900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-89900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-281700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-275400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>589100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-26400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>475300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-77800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-428100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-51400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-145100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E101" s="3">
         <v>8100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6600</v>
-      </c>
-      <c r="F101" s="3">
-        <v>3500</v>
       </c>
       <c r="G101" s="3">
         <v>3500</v>
       </c>
       <c r="H101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I101" s="3">
         <v>9800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-16600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1200</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-344000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-203400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-296100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>898400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-59700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-219000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-883900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-140700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>496600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>514300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>184600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>46000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-142200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>416100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-245300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>EDR</t>
   </si>
@@ -656,289 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1850300</v>
+        <v>1751300</v>
       </c>
       <c r="E8" s="3">
+        <v>1759600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1582700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1344400</v>
       </c>
-      <c r="G8" s="3">
-        <v>3033000</v>
-      </c>
       <c r="H8" s="3">
-        <v>1596800</v>
+        <v>1305600</v>
       </c>
       <c r="I8" s="3">
+        <v>1496000</v>
+      </c>
+      <c r="J8" s="3">
         <v>1260400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1221400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1312500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1473800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1505600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1391300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1111300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1069600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4571000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1038800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1009700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1213700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>898900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>780700</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>844600</v>
+        <v>742000</v>
       </c>
       <c r="E9" s="3">
+        <v>790800</v>
+      </c>
+      <c r="F9" s="3">
         <v>645400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>487900</v>
       </c>
-      <c r="G9" s="3">
-        <v>1308300</v>
-      </c>
       <c r="H9" s="3">
-        <v>724300</v>
+        <v>515900</v>
       </c>
       <c r="I9" s="3">
+        <v>671600</v>
+      </c>
+      <c r="J9" s="3">
         <v>464200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>398500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>508400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>694600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>806600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>673200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>571000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>546400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2323300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>513500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>572400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1722100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1005700</v>
+        <v>1009300</v>
       </c>
       <c r="E10" s="3">
+        <v>968800</v>
+      </c>
+      <c r="F10" s="3">
         <v>937300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>856500</v>
       </c>
-      <c r="G10" s="3">
-        <v>1724700</v>
-      </c>
       <c r="H10" s="3">
-        <v>872500</v>
+        <v>789700</v>
       </c>
       <c r="I10" s="3">
+        <v>824400</v>
+      </c>
+      <c r="J10" s="3">
         <v>796200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>822900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>804100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>779200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>699000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>718100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>540300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>523200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2247700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>525300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>437300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-508400</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>445600</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,8 +974,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,56 +1102,59 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>64200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-690300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>28200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-23300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-463600</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>2500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1147,70 +1167,76 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>156300</v>
+        <v>138600</v>
       </c>
       <c r="E15" s="3">
+        <v>142500</v>
+      </c>
+      <c r="F15" s="3">
         <v>152500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>81200</v>
       </c>
-      <c r="G15" s="3">
-        <v>127800</v>
-      </c>
       <c r="H15" s="3">
-        <v>66800</v>
+        <v>49800</v>
       </c>
       <c r="I15" s="3">
+        <v>55300</v>
+      </c>
+      <c r="J15" s="3">
         <v>71600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>63600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>65600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>74800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>71700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>69200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>67200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>280700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>64800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>78500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>366000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2161400</v>
+        <v>1639800</v>
       </c>
       <c r="E17" s="3">
+        <v>1979200</v>
+      </c>
+      <c r="F17" s="3">
         <v>853100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1312500</v>
       </c>
-      <c r="G17" s="3">
-        <v>2738000</v>
-      </c>
       <c r="H17" s="3">
-        <v>1460200</v>
+        <v>1151000</v>
       </c>
       <c r="I17" s="3">
+        <v>1354700</v>
+      </c>
+      <c r="J17" s="3">
         <v>1142300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1064200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1161500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>836200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1452100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1254000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1447400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>975100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4360400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1005900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1032300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3720900</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-311100</v>
+        <v>111500</v>
       </c>
       <c r="E18" s="3">
+        <v>-219600</v>
+      </c>
+      <c r="F18" s="3">
         <v>729600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>31900</v>
       </c>
-      <c r="G18" s="3">
-        <v>295000</v>
-      </c>
       <c r="H18" s="3">
-        <v>136600</v>
+        <v>154600</v>
       </c>
       <c r="I18" s="3">
+        <v>141300</v>
+      </c>
+      <c r="J18" s="3">
         <v>118100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>157200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>151000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>637600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>53500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>137300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-336100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>94500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>210600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-22600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2507200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>-62800</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,318 +1411,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5400</v>
+        <v>700</v>
       </c>
       <c r="E20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-658000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-33200</v>
       </c>
-      <c r="G20" s="3">
-        <v>778700</v>
-      </c>
       <c r="H20" s="3">
+        <v>752300</v>
+      </c>
+      <c r="I20" s="3">
         <v>26800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-822900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-57200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-94500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-69300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>19400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-61700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2457300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-160100</v>
+        <v>236800</v>
       </c>
       <c r="E21" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="F21" s="3">
         <v>224100</v>
       </c>
-      <c r="F21" s="3">
-        <v>79900</v>
-      </c>
       <c r="G21" s="3">
-        <v>1201500</v>
+        <v>102600</v>
       </c>
       <c r="H21" s="3">
-        <v>230100</v>
+        <v>945200</v>
       </c>
       <c r="I21" s="3">
+        <v>234900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-633100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>219700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>212900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>646400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>33800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>201200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-259000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>158500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>422100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>117100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>96600</v>
+        <v>97600</v>
       </c>
       <c r="E22" s="3">
+        <v>96800</v>
+      </c>
+      <c r="F22" s="3">
         <v>88300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>82000</v>
       </c>
-      <c r="G22" s="3">
-        <v>175400</v>
-      </c>
       <c r="H22" s="3">
-        <v>85100</v>
+        <v>90400</v>
       </c>
       <c r="I22" s="3">
+        <v>85200</v>
+      </c>
+      <c r="J22" s="3">
         <v>84900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>75600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>62500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>59300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>60700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>55800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>83800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>68400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>270900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>70700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>71400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>277200</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-413000</v>
+        <v>14600</v>
       </c>
       <c r="E23" s="3">
+        <v>-320800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-16700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-83200</v>
       </c>
-      <c r="G23" s="3">
-        <v>898200</v>
-      </c>
       <c r="H23" s="3">
-        <v>78300</v>
+        <v>816500</v>
       </c>
       <c r="I23" s="3">
+        <v>83000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-789600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>80500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>84800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>521100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-101700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-412000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-129600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-155600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-327100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>-151500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-111800</v>
+        <v>-143400</v>
       </c>
       <c r="E24" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="F24" s="3">
         <v>13900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30000</v>
       </c>
-      <c r="G24" s="3">
-        <v>175900</v>
-      </c>
       <c r="H24" s="3">
-        <v>35500</v>
+        <v>139800</v>
       </c>
       <c r="I24" s="3">
+        <v>34900</v>
+      </c>
+      <c r="J24" s="3">
         <v>-642500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-17200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-80600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>60900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-22400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>88200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>87900</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-301200</v>
+        <v>158000</v>
       </c>
       <c r="E26" s="3">
+        <v>-257300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-30600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-113200</v>
       </c>
-      <c r="G26" s="3">
-        <v>722300</v>
-      </c>
       <c r="H26" s="3">
-        <v>42800</v>
+        <v>676700</v>
       </c>
       <c r="I26" s="3">
+        <v>48100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-147100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>72000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>82100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>538300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>81500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-473000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-133000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-32100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-133200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-415300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>-239400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-137300</v>
+        <v>194400</v>
       </c>
       <c r="E27" s="3">
+        <v>-93100</v>
+      </c>
+      <c r="F27" s="3">
         <v>17300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-69200</v>
       </c>
-      <c r="G27" s="3">
-        <v>408800</v>
-      </c>
       <c r="H27" s="3">
-        <v>2400</v>
+        <v>400300</v>
       </c>
       <c r="I27" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J27" s="3">
         <v>-206200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>319500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-319600</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-548800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-52900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-134700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-378500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>-243800</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,34 +1994,37 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-408900</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>-43900</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+        <v>-5300</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -1980,26 +2041,29 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>-5000</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>-5000</v>
       </c>
       <c r="S29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>695000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3">
         <v>-50200</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2189,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5400</v>
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F32" s="3">
         <v>658000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>33200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-778700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-752300</v>
+      </c>
+      <c r="I32" s="3">
         <v>-26800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>822900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>57200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>94500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>69300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-19400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>61700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2457300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-137300</v>
+        <v>-214500</v>
       </c>
       <c r="E33" s="3">
+        <v>-137100</v>
+      </c>
+      <c r="F33" s="3">
         <v>17300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-69200</v>
       </c>
-      <c r="G33" s="3">
-        <v>408800</v>
-      </c>
       <c r="H33" s="3">
+        <v>403200</v>
+      </c>
+      <c r="I33" s="3">
         <v>2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-206200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>319500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-319600</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-553800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-57900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-134700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>316500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-137300</v>
+        <v>-214500</v>
       </c>
       <c r="E35" s="3">
+        <v>-137100</v>
+      </c>
+      <c r="F35" s="3">
         <v>17300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-69200</v>
       </c>
-      <c r="G35" s="3">
-        <v>408800</v>
-      </c>
       <c r="H35" s="3">
+        <v>403200</v>
+      </c>
+      <c r="I35" s="3">
         <v>2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-206200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>319500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-319600</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-553800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-57900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-134700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>316500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,70 +2571,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>697700</v>
+      </c>
+      <c r="E41" s="3">
         <v>778600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1166500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1337700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1616500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>718700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>767800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>970800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1824000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2030300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1561000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1028700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>869800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>880900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>705300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>830900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>499700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,70 +2699,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1008800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1087900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>939800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1083100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>982200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>991600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>917000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>893400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>826700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>760500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>615000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>639400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>597600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>519500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>779500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>806900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>789600</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2733,318 +2829,336 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1698300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1536500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1358200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1266300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1009500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>827900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>851900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>823000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>810300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>625400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1577700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1642000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>619300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>551400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>536900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>518500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>511000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3404700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3403000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3464500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3687100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3608100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2538200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2536700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2687100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3461000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3416200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3753700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3310100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2086700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1951700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2021800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2156300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1800400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>397100</v>
+      </c>
+      <c r="E47" s="3">
         <v>404200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>398000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>387000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>344000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>348500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>337000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>407400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>483600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>492700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>298200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>285800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>295000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>225100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>580100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>920200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1178900</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1278100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1386000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1265300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1221800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>801500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1049000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1042900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>967200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>987700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>991500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1003500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>961500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>963500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>979400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1025200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1002500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>973800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14131500</v>
+      </c>
+      <c r="E49" s="3">
         <v>15180900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15364200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15461700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7258300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7492100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7490300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7437600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6456600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6132200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6118200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5970000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5992000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5731800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5494500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5572700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5637700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,70 +3284,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1949700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1138600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1052700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1144000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1304600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1191800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1097000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>416500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>347800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>326700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>260900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>203400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>966900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>719800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>170800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>351900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>294600</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21161100</v>
+      </c>
+      <c r="E54" s="3">
         <v>21512700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21544800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21901600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13316600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12619700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12503800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11915900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11736600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11359400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11434500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10730900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10304100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9607700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9292300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10003600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9885300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,380 +3531,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>531300</v>
+      </c>
+      <c r="E57" s="3">
         <v>608900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>587600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>590100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>673700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>615200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>540100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>527400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>558900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>556200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>522100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>497200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>509500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>451700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>460500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2329600</v>
+      </c>
+      <c r="E58" s="3">
         <v>54800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>58900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>99000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>88700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>88300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>89000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>87100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>82600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>82000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>75900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>94800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>103200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>115400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>107700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>93300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2648500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2264200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2150400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2269700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1860700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1839100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1725600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1719600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1581600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1388700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2064600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2075100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1548500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1317100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1188200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1466000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1280400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5509400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2927800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2796900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2922800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2633400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2543000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2414500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2348800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2268700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1998800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2705400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2707100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2165500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1917500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1813100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2025400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1834200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2743000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4955400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4969400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4983400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5011400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5062500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5080200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5338400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5596700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5621400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5631700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5032500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5255700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5768300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4929900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4491600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4525200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2075900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2215900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2055900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2125700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1574600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1617200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1702500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>805200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>745900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>772700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>766000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>736500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>753500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>747600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>681200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>718500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>660200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16735400</v>
+      </c>
+      <c r="E66" s="3">
         <v>16850700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16760100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17138600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10812200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10594900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10623000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9925400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9835800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9689000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10187500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9523100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9165400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9312100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8335300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8613000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8385600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,50 +4464,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-505400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-272500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-117100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-52200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>195000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-208200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-216200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10000</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
       <c r="L72" s="3">
+        <v>0</v>
+      </c>
+      <c r="M72" s="3">
         <v>22900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-296600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-277100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-319600</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4349,14 +4523,17 @@
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4425700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4662100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4784700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4763100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2504300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2024800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1880800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1990500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1900800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1670300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1247000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1207700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1138700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>295600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>957000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1390600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1499800</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-137300</v>
+        <v>-214500</v>
       </c>
       <c r="E81" s="3">
+        <v>-137100</v>
+      </c>
+      <c r="F81" s="3">
         <v>17300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-69200</v>
       </c>
-      <c r="G81" s="3">
-        <v>408800</v>
-      </c>
       <c r="H81" s="3">
+        <v>403200</v>
+      </c>
+      <c r="I81" s="3">
         <v>2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-206200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>319500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-319600</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-553800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-57900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-134700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>316500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5016,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>124700</v>
+      </c>
+      <c r="E83" s="3">
         <v>156300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>152500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>81200</v>
       </c>
-      <c r="G83" s="3">
-        <v>127800</v>
-      </c>
       <c r="H83" s="3">
+        <v>61100</v>
+      </c>
+      <c r="I83" s="3">
         <v>66800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>63600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>65600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>66000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>74800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>71700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>69200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>280700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>78500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>401100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-136300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>105800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>94500</v>
       </c>
-      <c r="G89" s="3">
-        <v>197400</v>
-      </c>
       <c r="H89" s="3">
+        <v>96600</v>
+      </c>
+      <c r="I89" s="3">
         <v>100800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>96400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>189300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>271200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-29400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>176300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>250800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-51400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-70800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>392900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>315800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-59000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5496,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-72800</v>
       </c>
-      <c r="F91" s="3">
-        <v>-53700</v>
-      </c>
       <c r="G91" s="3">
-        <v>-56000</v>
+        <v>-70700</v>
       </c>
       <c r="H91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-55100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-53200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-58800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-135400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-38900</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-72900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-58100</v>
       </c>
-      <c r="G94" s="3">
-        <v>861400</v>
-      </c>
       <c r="H94" s="3">
+        <v>935500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-74100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-784200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-421600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>544700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-250500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-380200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>7600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>46100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>153300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-42500</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5781,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5560,20 +5794,20 @@
         <v>-27100</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-27100</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-27400</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-10100</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -5581,37 +5815,40 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-121000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-12100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-37000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,190 +6039,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-340500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-131500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-244300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-326000</v>
       </c>
-      <c r="G100" s="3">
-        <v>-163900</v>
-      </c>
       <c r="H100" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-89900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-281700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-275400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>26300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-19100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>589100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-26400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>475300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-77800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-428100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-51400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-145100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>3500</v>
       </c>
-      <c r="H101" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-16600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1200</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-344000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-203400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-296100</v>
       </c>
-      <c r="G102" s="3">
-        <v>898400</v>
-      </c>
       <c r="H102" s="3">
+        <v>958100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-59700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-219000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-883900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-140700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>496600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>514300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>184600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>46000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-142200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>416100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-245300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>EDR</t>
   </si>
@@ -656,302 +656,315 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1751300</v>
-      </c>
-      <c r="E8" s="3">
+        <v>2031800</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>1759600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1582700</v>
       </c>
-      <c r="G8" s="3">
-        <v>1344400</v>
-      </c>
       <c r="H8" s="3">
-        <v>1305600</v>
-      </c>
-      <c r="I8" s="3">
+        <v>1219500</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
         <v>1496000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1260400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1221400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1312500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1473800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1505600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1391300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1111300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1069600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4571000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1038800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1009700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1213700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>898900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>780700</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>742000</v>
-      </c>
-      <c r="E9" s="3">
+        <v>1097600</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
         <v>790800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>645400</v>
       </c>
-      <c r="G9" s="3">
-        <v>487900</v>
-      </c>
       <c r="H9" s="3">
-        <v>515900</v>
-      </c>
-      <c r="I9" s="3">
+        <v>431100</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
         <v>671600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>464200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>398500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>508400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>694600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>806600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>673200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>571000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>546400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2323300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>513500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>572400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1722100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1009300</v>
-      </c>
-      <c r="E10" s="3">
+        <v>934200</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
         <v>968800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>937300</v>
       </c>
-      <c r="G10" s="3">
-        <v>856500</v>
-      </c>
       <c r="H10" s="3">
-        <v>789700</v>
-      </c>
-      <c r="I10" s="3">
+        <v>788500</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
         <v>824400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>796200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>822900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>804100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>779200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>699000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>718100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>540300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>523200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2247700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>525300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>437300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-508400</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>445600</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +988,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1054,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,59 +1122,62 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>64200</v>
+      <c r="D14" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
-        <v>-690300</v>
+        <v>-354800</v>
       </c>
       <c r="G14" s="3">
+        <v>47700</v>
+      </c>
+      <c r="H14" s="3">
         <v>28200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K14" s="3">
         <v>-23300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-463600</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>32400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>2500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1170,73 +1190,79 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>138600</v>
+        <v>135500</v>
       </c>
       <c r="E15" s="3">
+        <v>137400</v>
+      </c>
+      <c r="F15" s="3">
         <v>142500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>152500</v>
       </c>
-      <c r="G15" s="3">
-        <v>81200</v>
-      </c>
       <c r="H15" s="3">
-        <v>49800</v>
+        <v>66600</v>
       </c>
       <c r="I15" s="3">
+        <v>60600</v>
+      </c>
+      <c r="J15" s="3">
         <v>55300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>71600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>65600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>66000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>74800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>71700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>69200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>67200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>280700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>64800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>78500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>366000</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1283,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1639800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1979200</v>
+        <v>2024800</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F17" s="3">
-        <v>853100</v>
+        <v>2334100</v>
       </c>
       <c r="G17" s="3">
-        <v>1312500</v>
+        <v>1533900</v>
       </c>
       <c r="H17" s="3">
-        <v>1151000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1354700</v>
+        <v>1169200</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J17" s="3">
+        <v>1354800</v>
+      </c>
+      <c r="K17" s="3">
         <v>1142300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1064200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1161500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>836200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1452100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1254000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1447400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>975100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4360400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1005900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1032300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3720900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>111500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-219600</v>
+        <v>7000</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F18" s="3">
-        <v>729600</v>
+        <v>-574400</v>
       </c>
       <c r="G18" s="3">
-        <v>31900</v>
+        <v>48800</v>
       </c>
       <c r="H18" s="3">
-        <v>154600</v>
-      </c>
-      <c r="I18" s="3">
-        <v>141300</v>
+        <v>50400</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J18" s="3">
+        <v>141100</v>
+      </c>
+      <c r="K18" s="3">
         <v>118100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>157200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>151000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>637600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>53500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>137300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-336100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>94500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>210600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-22600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2507200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>-62800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,333 +1445,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-4400</v>
+        <v>-22600</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F20" s="3">
-        <v>-658000</v>
+        <v>6600</v>
       </c>
       <c r="G20" s="3">
-        <v>-33200</v>
+        <v>-71800</v>
       </c>
       <c r="H20" s="3">
-        <v>752300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>26800</v>
+        <v>36000</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J20" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-822900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-57200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-94500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-69300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-61700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2457300</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>236800</v>
+        <v>165100</v>
       </c>
       <c r="E21" s="3">
-        <v>-67600</v>
+        <v>137400</v>
       </c>
       <c r="F21" s="3">
-        <v>224100</v>
+        <v>-438500</v>
       </c>
       <c r="G21" s="3">
-        <v>102600</v>
+        <v>273100</v>
       </c>
       <c r="H21" s="3">
-        <v>945200</v>
+        <v>80900</v>
       </c>
       <c r="I21" s="3">
-        <v>234900</v>
+        <v>60600</v>
       </c>
       <c r="J21" s="3">
+        <v>216000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-633100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>219700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>212900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>646400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>33800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>201200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-259000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>158500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>422100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>117100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5700</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>97600</v>
-      </c>
-      <c r="E22" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
         <v>96800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>88300</v>
       </c>
-      <c r="G22" s="3">
-        <v>82000</v>
-      </c>
       <c r="H22" s="3">
-        <v>90400</v>
-      </c>
-      <c r="I22" s="3">
+        <v>82300</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
         <v>85200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>84900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>75600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>62500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>59300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>60700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>55800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>83800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>68400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>270900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>70700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>71400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>277200</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>14600</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-320800</v>
+        <v>-72500</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F23" s="3">
-        <v>-16700</v>
+        <v>-323000</v>
       </c>
       <c r="G23" s="3">
-        <v>-83200</v>
+        <v>-15400</v>
       </c>
       <c r="H23" s="3">
-        <v>816500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>83000</v>
+        <v>-96100</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J23" s="3">
+        <v>76400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-789600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>80500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>84800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>521100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-101700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>73800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-412000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-129600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-155600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-327100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>-151500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-143400</v>
-      </c>
-      <c r="E24" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
         <v>-63500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13900</v>
       </c>
-      <c r="G24" s="3">
-        <v>30000</v>
-      </c>
       <c r="H24" s="3">
-        <v>139800</v>
-      </c>
-      <c r="I24" s="3">
+        <v>20900</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
         <v>34900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-642500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-17200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-80600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>60900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>13700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-22400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>88200</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>87900</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1851,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>158000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-257300</v>
+        <v>-186300</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F26" s="3">
-        <v>-30600</v>
+        <v>-259500</v>
       </c>
       <c r="G26" s="3">
-        <v>-113200</v>
+        <v>-29300</v>
       </c>
       <c r="H26" s="3">
-        <v>676700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>48100</v>
+        <v>-117000</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J26" s="3">
+        <v>41600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-147100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>72000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>82100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>538300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>81500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-473000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-133000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-32100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-133200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-415300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>-239400</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>194400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-93100</v>
+        <v>-264700</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F27" s="3">
+        <v>-137100</v>
+      </c>
+      <c r="G27" s="3">
         <v>17300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-69200</v>
       </c>
-      <c r="H27" s="3">
-        <v>400300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>7700</v>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J27" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-206200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>319500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-319600</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-548800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-52900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-134700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-378500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>-243800</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,37 +2055,40 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-408900</v>
+        <v>-234100</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-43900</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>2800</v>
+        <v>1000</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-5300</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -2044,26 +2105,29 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>-5000</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>-5000</v>
       </c>
       <c r="T29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>695000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>-50200</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2259,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>4400</v>
+        <v>22600</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F32" s="3">
-        <v>658000</v>
+        <v>-6600</v>
       </c>
       <c r="G32" s="3">
-        <v>33200</v>
+        <v>71800</v>
       </c>
       <c r="H32" s="3">
-        <v>-752300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-26800</v>
+        <v>-36000</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J32" s="3">
+        <v>19600</v>
+      </c>
+      <c r="K32" s="3">
         <v>822900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>57200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>94500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>69300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>61700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2457300</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-214500</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-137100</v>
+        <v>-264700</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F33" s="3">
-        <v>17300</v>
+        <v>-137300</v>
       </c>
       <c r="G33" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H33" s="3">
         <v>-69200</v>
       </c>
-      <c r="H33" s="3">
-        <v>403200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2400</v>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-206200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>319500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>42500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-319600</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-553800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-57900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-134700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>316500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2463,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-214500</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-137100</v>
+        <v>-264700</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F35" s="3">
-        <v>17300</v>
+        <v>-137300</v>
       </c>
       <c r="G35" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H35" s="3">
         <v>-69200</v>
       </c>
-      <c r="H35" s="3">
-        <v>403200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2400</v>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-206200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>319500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>42500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-319600</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-553800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-57900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-134700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>316500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2658,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1004100</v>
+      </c>
+      <c r="E41" s="3">
         <v>697700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>778600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1166500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1337700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1616500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>718700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>767800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>970800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1824000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2030300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1561000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1028700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>869800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>880900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>705300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>830900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>499700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,96 +2792,102 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1008800</v>
+        <v>1055700</v>
       </c>
       <c r="E43" s="3">
-        <v>1087900</v>
+        <v>1025000</v>
       </c>
       <c r="F43" s="3">
-        <v>939800</v>
+        <v>1099300</v>
       </c>
       <c r="G43" s="3">
-        <v>1083100</v>
+        <v>951600</v>
       </c>
       <c r="H43" s="3">
-        <v>982200</v>
+        <v>1102900</v>
       </c>
       <c r="I43" s="3">
-        <v>991600</v>
+        <v>999600</v>
       </c>
       <c r="J43" s="3">
+        <v>1009200</v>
+      </c>
+      <c r="K43" s="3">
         <v>917000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>893400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>826700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>760500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>615000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>639400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>597600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>519500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>779500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>806900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>789600</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2832,333 +2928,351 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1698300</v>
+        <v>959800</v>
       </c>
       <c r="E45" s="3">
-        <v>1536500</v>
+        <v>1278700</v>
       </c>
       <c r="F45" s="3">
-        <v>1358200</v>
+        <v>1202700</v>
       </c>
       <c r="G45" s="3">
-        <v>1266300</v>
+        <v>1067900</v>
       </c>
       <c r="H45" s="3">
-        <v>1009500</v>
+        <v>935900</v>
       </c>
       <c r="I45" s="3">
-        <v>827900</v>
+        <v>664200</v>
       </c>
       <c r="J45" s="3">
+        <v>542700</v>
+      </c>
+      <c r="K45" s="3">
         <v>851900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>823000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>810300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>625400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1577700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1642000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>619300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>551400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>536900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>518500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>511000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3344800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3404700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3403000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3464500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3687100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3608100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2538200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2536700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2687100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3461000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3416200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3753700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3310100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2086700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1951700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2021800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2156300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1800400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E47" s="3">
         <v>397100</v>
       </c>
-      <c r="E47" s="3">
-        <v>404200</v>
-      </c>
       <c r="F47" s="3">
-        <v>398000</v>
+        <v>424000</v>
       </c>
       <c r="G47" s="3">
-        <v>387000</v>
+        <v>430700</v>
       </c>
       <c r="H47" s="3">
-        <v>344000</v>
+        <v>440700</v>
       </c>
       <c r="I47" s="3">
-        <v>348500</v>
+        <v>410000</v>
       </c>
       <c r="J47" s="3">
+        <v>408900</v>
+      </c>
+      <c r="K47" s="3">
         <v>337000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>407400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>483600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>492700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>298200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>285800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>295000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>225100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>580100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>920200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1178900</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1505300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1278100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1386000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1265300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1221800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>801500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1049000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1042900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>967200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>987700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>991500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1003500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>961500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>963500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>979400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1025200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1002500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>973800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14077700</v>
+      </c>
+      <c r="E49" s="3">
         <v>14131500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15180900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15364200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15461700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7258300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7492100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7490300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7437600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6456600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6132200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6118200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5970000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5992000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5731800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5494500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5572700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5637700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,73 +3404,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1949700</v>
+        <v>966500</v>
       </c>
       <c r="E52" s="3">
-        <v>1138600</v>
+        <v>1503200</v>
       </c>
       <c r="F52" s="3">
-        <v>1052700</v>
+        <v>655700</v>
       </c>
       <c r="G52" s="3">
-        <v>1144000</v>
+        <v>559300</v>
       </c>
       <c r="H52" s="3">
-        <v>1304600</v>
+        <v>491200</v>
       </c>
       <c r="I52" s="3">
-        <v>1191800</v>
+        <v>398700</v>
       </c>
       <c r="J52" s="3">
+        <v>326400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1097000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>416500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>347800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>326700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>260900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>203400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>966900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>719800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>170800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>351900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>294600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3540,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20777900</v>
+      </c>
+      <c r="E54" s="3">
         <v>21161100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21512700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21544800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21901600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13316600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12619700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12503800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11915900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11736600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11359400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11434500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10730900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10304100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9607700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9292300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10003600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9885300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,398 +3662,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>541400</v>
+      </c>
+      <c r="E57" s="3">
         <v>531300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>608900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>587600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>590100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>673700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>615200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>540100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>527400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>558900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>556200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>522100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>497200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>509500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>451700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>460500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2329600</v>
+        <v>2391500</v>
       </c>
       <c r="E58" s="3">
-        <v>54800</v>
+        <v>2395200</v>
       </c>
       <c r="F58" s="3">
-        <v>58900</v>
+        <v>123000</v>
       </c>
       <c r="G58" s="3">
-        <v>63000</v>
+        <v>143300</v>
       </c>
       <c r="H58" s="3">
-        <v>99000</v>
+        <v>142700</v>
       </c>
       <c r="I58" s="3">
-        <v>88700</v>
+        <v>169300</v>
       </c>
       <c r="J58" s="3">
+        <v>157400</v>
+      </c>
+      <c r="K58" s="3">
         <v>88300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>89000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>87100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>82600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>82000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>75900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>94800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>103200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>115400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>107700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>93300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2648500</v>
+        <v>1575700</v>
       </c>
       <c r="E59" s="3">
-        <v>2264200</v>
+        <v>1938500</v>
       </c>
       <c r="F59" s="3">
-        <v>2150400</v>
+        <v>1357600</v>
       </c>
       <c r="G59" s="3">
-        <v>2269700</v>
+        <v>1355400</v>
       </c>
       <c r="H59" s="3">
-        <v>1860700</v>
+        <v>1476800</v>
       </c>
       <c r="I59" s="3">
-        <v>1839100</v>
+        <v>1283700</v>
       </c>
       <c r="J59" s="3">
+        <v>1233800</v>
+      </c>
+      <c r="K59" s="3">
         <v>1725600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1719600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1581600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1388700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2064600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2075100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1548500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1317100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1188200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1466000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1280400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5271100</v>
+      </c>
+      <c r="E60" s="3">
         <v>5509400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2927800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2796900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2922800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2633400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2543000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2414500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2348800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2268700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1998800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2705400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2707100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2165500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1917500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1813100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2025400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1834200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2743000</v>
+        <v>3283200</v>
       </c>
       <c r="E61" s="3">
-        <v>4955400</v>
+        <v>3135000</v>
       </c>
       <c r="F61" s="3">
-        <v>4969400</v>
+        <v>5365300</v>
       </c>
       <c r="G61" s="3">
-        <v>4983400</v>
+        <v>5502300</v>
       </c>
       <c r="H61" s="3">
-        <v>5011400</v>
+        <v>5517500</v>
       </c>
       <c r="I61" s="3">
-        <v>5062500</v>
+        <v>5316200</v>
       </c>
       <c r="J61" s="3">
+        <v>5377100</v>
+      </c>
+      <c r="K61" s="3">
         <v>5080200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5338400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5596700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5621400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5631700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5032500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5255700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5768300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4929900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4491600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4525200</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2075900</v>
+        <v>1237000</v>
       </c>
       <c r="E62" s="3">
-        <v>2215900</v>
+        <v>1187700</v>
       </c>
       <c r="F62" s="3">
-        <v>2055900</v>
+        <v>1234700</v>
       </c>
       <c r="G62" s="3">
-        <v>2125700</v>
+        <v>971000</v>
       </c>
       <c r="H62" s="3">
-        <v>1574600</v>
+        <v>1002600</v>
       </c>
       <c r="I62" s="3">
-        <v>1617200</v>
+        <v>1149300</v>
       </c>
       <c r="J62" s="3">
+        <v>1181500</v>
+      </c>
+      <c r="K62" s="3">
         <v>1702500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>805200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>745900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>772700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>766000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>736500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>753500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>747600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>681200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>718500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>660200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4272,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16735400</v>
+        <v>10289000</v>
       </c>
       <c r="E66" s="3">
-        <v>16850700</v>
+        <v>10328300</v>
       </c>
       <c r="F66" s="3">
-        <v>16760100</v>
+        <v>10099100</v>
       </c>
       <c r="G66" s="3">
-        <v>17138600</v>
+        <v>9822300</v>
       </c>
       <c r="H66" s="3">
-        <v>10812200</v>
+        <v>10031900</v>
       </c>
       <c r="I66" s="3">
-        <v>10594900</v>
+        <v>9219400</v>
       </c>
       <c r="J66" s="3">
+        <v>9222700</v>
+      </c>
+      <c r="K66" s="3">
         <v>10623000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9925400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9835800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9689000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10187500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9523100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9165400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9312100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8335300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8613000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8385600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,53 +4638,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-788500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-505400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-272500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-117100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-52200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>195000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-208200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-216200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-10000</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
       <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3">
         <v>22900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-296600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-277100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-319600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4526,14 +4700,17 @@
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4910,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4224800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4425700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4662100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4784700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4763100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2504300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2024800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1880800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1990500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1900800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1670300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1247000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1207700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1138700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>295600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>957000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1390600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1499800</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5046,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-214500</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-137100</v>
+        <v>-264700</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F81" s="3">
-        <v>17300</v>
+        <v>-137300</v>
       </c>
       <c r="G81" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H81" s="3">
         <v>-69200</v>
       </c>
-      <c r="H81" s="3">
-        <v>403200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2400</v>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-206200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>319500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>42500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-319600</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-553800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-57900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-134700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>316500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,73 +5215,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>124700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>156300</v>
+        <v>73100</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F83" s="3">
-        <v>152500</v>
+        <v>25600</v>
       </c>
       <c r="G83" s="3">
-        <v>81200</v>
+        <v>25200</v>
       </c>
       <c r="H83" s="3">
-        <v>61100</v>
+        <v>24500</v>
       </c>
       <c r="I83" s="3">
-        <v>66800</v>
+        <v>24200</v>
       </c>
       <c r="J83" s="3">
+        <v>23100</v>
+      </c>
+      <c r="K83" s="3">
         <v>71600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>63600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>65600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>66000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>74800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>71700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>69200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>67200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>280700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>78500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5621,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>401100</v>
-      </c>
-      <c r="E89" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>-136300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>105800</v>
       </c>
-      <c r="G89" s="3">
-        <v>94500</v>
-      </c>
       <c r="H89" s="3">
-        <v>96600</v>
-      </c>
-      <c r="I89" s="3">
-        <v>100800</v>
+        <v>85500</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J89" s="3">
+        <v>96700</v>
+      </c>
+      <c r="K89" s="3">
         <v>96400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>189300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>271200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-29400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>176300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>250800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-70800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>392900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>315800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-59000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5717,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-28800</v>
-      </c>
-      <c r="E91" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-62800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-72800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-70700</v>
-      </c>
       <c r="H91" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-39000</v>
       </c>
-      <c r="I91" s="3">
-        <v>-55100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-53200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-58800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-135400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-31100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-38900</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5919,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-60000</v>
-      </c>
-      <c r="E94" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>-72200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-72900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-58100</v>
-      </c>
       <c r="H94" s="3">
-        <v>935500</v>
-      </c>
-      <c r="I94" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
         <v>-74100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-43500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-784200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-421600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>544700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-250500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-36100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-380200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>7600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>46100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>153300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,35 +6015,36 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-27100</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-27100</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
-        <v>-27100</v>
+        <v>18100</v>
       </c>
       <c r="G96" s="3">
-        <v>-27400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+        <v>18100</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3">
         <v>-10100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -5818,37 +6052,40 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-5200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-121000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-37000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,199 +6285,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-340500</v>
-      </c>
-      <c r="E100" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>-131500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-244300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-326000</v>
       </c>
-      <c r="H100" s="3">
-        <v>-74000</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
         <v>-89900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-281700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-275400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>26300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>589100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-26400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>475300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-77800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-428100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-51400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-145100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>9800</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>300</v>
+      </c>
+      <c r="K101" s="3">
+        <v>9800</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="N101" s="3">
+        <v>300</v>
+      </c>
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="F101" s="3">
-        <v>8100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>9800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-16600</v>
-      </c>
-      <c r="M101" s="3">
-        <v>300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>228300</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-344000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-203400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-296100</v>
       </c>
-      <c r="H102" s="3">
-        <v>958100</v>
-      </c>
       <c r="I102" s="3">
-        <v>-59700</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-219000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-883900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-140700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>496600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>514300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>184600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>46000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-142200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>416100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-245300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EDR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>EDR</t>
   </si>
@@ -656,315 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1568300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2031800</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
         <v>1759600</v>
       </c>
-      <c r="G8" s="3">
-        <v>1582700</v>
-      </c>
       <c r="H8" s="3">
+        <v>1469600</v>
+      </c>
+      <c r="I8" s="3">
         <v>1219500</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>1496000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1260400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1221400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1312500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1473800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1505600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1391300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1111300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1069600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4571000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1038800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1009700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1213700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>898900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>780700</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>667300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1097600</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
         <v>790800</v>
       </c>
-      <c r="G9" s="3">
-        <v>645400</v>
-      </c>
       <c r="H9" s="3">
+        <v>593400</v>
+      </c>
+      <c r="I9" s="3">
         <v>431100</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>671600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>464200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>398500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>508400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>694600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>806600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>673200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>571000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>546400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2323300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>513500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>572400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1722100</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>335100</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>901000</v>
+      </c>
+      <c r="E10" s="3">
         <v>934200</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
         <v>968800</v>
       </c>
-      <c r="G10" s="3">
-        <v>937300</v>
-      </c>
       <c r="H10" s="3">
+        <v>876200</v>
+      </c>
+      <c r="I10" s="3">
         <v>788500</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>824400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>796200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>822900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>804100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>779200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>699000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>718100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>540300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>523200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2247700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>525300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>437300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-508400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>445600</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,62 +1141,65 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-6000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-354800</v>
       </c>
-      <c r="G14" s="3">
-        <v>47700</v>
-      </c>
       <c r="H14" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I14" s="3">
         <v>28200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>-900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-23300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-463600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>32400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1193,76 +1212,82 @@
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E15" s="3">
         <v>135500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>137400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>142500</v>
       </c>
-      <c r="G15" s="3">
-        <v>152500</v>
-      </c>
       <c r="H15" s="3">
+        <v>138500</v>
+      </c>
+      <c r="I15" s="3">
         <v>66600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>55300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>71600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>63600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>65600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>66000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>74800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>71700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>69200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>67200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>280700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>64800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>78500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>366000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1544100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2024800</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
         <v>2334100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1533900</v>
-      </c>
       <c r="H17" s="3">
+        <v>1435500</v>
+      </c>
+      <c r="I17" s="3">
         <v>1169200</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>1354800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1142300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1064200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1161500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>836200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1452100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1254000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1447400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>975100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4360400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1005900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1032300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3720900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E18" s="3">
         <v>7000</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3">
         <v>-574400</v>
       </c>
-      <c r="G18" s="3">
-        <v>48800</v>
-      </c>
       <c r="H18" s="3">
+        <v>34100</v>
+      </c>
+      <c r="I18" s="3">
         <v>50400</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>141100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>118100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>157200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>151000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>637600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>53500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>137300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-336100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>94500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>210600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-22600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2507200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-62800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,348 +1478,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-22600</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
         <v>6600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-71800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="I20" s="3">
         <v>36000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-19600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-822900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-57200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-94500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-69300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>19400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-61700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2457300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-21600</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>109500</v>
+      </c>
+      <c r="E21" s="3">
         <v>165100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>137400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-438500</v>
       </c>
-      <c r="G21" s="3">
-        <v>273100</v>
-      </c>
       <c r="H21" s="3">
+        <v>243700</v>
+      </c>
+      <c r="I21" s="3">
         <v>80900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>60600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>216000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-633100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>219700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>212900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>646400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>201200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-259000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>158500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>422100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>117100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5700</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E22" s="3">
         <v>108100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
         <v>96800</v>
       </c>
-      <c r="G22" s="3">
-        <v>88300</v>
-      </c>
       <c r="H22" s="3">
+        <v>88400</v>
+      </c>
+      <c r="I22" s="3">
         <v>82300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>85200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>84900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>75600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>62500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>59300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>60700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>55800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>83800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>68400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>270900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>70700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>71400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>277200</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>67100</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-72500</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3">
         <v>-323000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-15400</v>
-      </c>
       <c r="H23" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-96100</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>76400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-789600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>80500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>84800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>521100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-101700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-412000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-129600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-155600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-327100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-151500</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E24" s="3">
         <v>113800</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
         <v>-63500</v>
       </c>
-      <c r="G24" s="3">
-        <v>13900</v>
-      </c>
       <c r="H24" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I24" s="3">
         <v>20900</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>34900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-642500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-17200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-80600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>88200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>87900</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-241400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-186300</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
         <v>-259500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-29300</v>
-      </c>
       <c r="H26" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-117000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>41600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-147100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>72000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>538300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>81500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-473000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-133000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-32100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-133200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-415300</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-239400</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-167200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-264700</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3">
         <v>-137100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-69200</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-206200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>319500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>42500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-319600</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-548800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-52900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-134700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-378500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-243800</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,40 +2115,43 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E29" s="3">
         <v>-234100</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-43900</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I29" s="3">
         <v>1000</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-5300</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
@@ -2108,26 +2168,29 @@
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
-        <v>-5000</v>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T29" s="3">
         <v>-5000</v>
       </c>
       <c r="U29" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>695000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-50200</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="E32" s="3">
         <v>22600</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
         <v>-6600</v>
       </c>
-      <c r="G32" s="3">
-        <v>71800</v>
-      </c>
       <c r="H32" s="3">
+        <v>71100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-36000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>19600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>822900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>57200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>94500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>69300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-19400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>61700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2457300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-165900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-264700</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3">
         <v>-137300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-69200</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>8000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-206200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>319500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>42500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-319600</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-553800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-57900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-134700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>316500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-165900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-264700</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3">
         <v>-137300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-69200</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>8000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-206200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>319500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>42500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-319600</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-553800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-57900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-134700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>316500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,76 +2744,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1201500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1004100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>697700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>778600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1166500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1337700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1616500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>718700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>767800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>970800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1824000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2030300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1561000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1028700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>869800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>880900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>705300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>830900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>499700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,76 +2884,82 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>897100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1055700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1025000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1099300</v>
       </c>
-      <c r="G43" s="3">
-        <v>951600</v>
-      </c>
       <c r="H43" s="3">
+        <v>822700</v>
+      </c>
+      <c r="I43" s="3">
         <v>1102900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>999600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1009200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>917000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>893400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>826700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>760500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>615000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>639400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>597600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>519500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>779500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>806900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>789600</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2889,8 +2984,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2931,348 +3026,366 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1578500</v>
+      </c>
+      <c r="E45" s="3">
         <v>959800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1278700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1202700</v>
       </c>
-      <c r="G45" s="3">
-        <v>1067900</v>
-      </c>
       <c r="H45" s="3">
+        <v>1196900</v>
+      </c>
+      <c r="I45" s="3">
         <v>935900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>664200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>542700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>851900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>823000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>810300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>625400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1577700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>619300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>551400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>536900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>518500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>511000</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4025800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3344800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3404700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3403000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3464500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3687100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3608100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2538200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2536700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2687100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3461000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3416200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3753700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3310100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2086700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1951700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2021800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2156300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1800400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>401700</v>
+      </c>
+      <c r="E47" s="3">
         <v>404700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>397100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>424000</v>
       </c>
-      <c r="G47" s="3">
-        <v>430700</v>
-      </c>
       <c r="H47" s="3">
+        <v>426900</v>
+      </c>
+      <c r="I47" s="3">
         <v>440700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>410000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>408900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>337000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>407400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>483600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>492700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>298200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>285800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>295000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>225100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>580100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>920200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1178900</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1429100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1505300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1278100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1386000</v>
       </c>
-      <c r="G48" s="3">
-        <v>1265300</v>
-      </c>
       <c r="H48" s="3">
+        <v>1224300</v>
+      </c>
+      <c r="I48" s="3">
         <v>1221800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>801500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1049000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1042900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>967200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>987700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>991500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1003500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>961500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>963500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>979400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1025200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1002500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>973800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13168000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14077700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14131500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15180900</v>
       </c>
-      <c r="G49" s="3">
-        <v>15364200</v>
-      </c>
       <c r="H49" s="3">
+        <v>14329400</v>
+      </c>
+      <c r="I49" s="3">
         <v>15461700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7258300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7492100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7490300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7437600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6456600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6132200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6118200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5970000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5992000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5731800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5494500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5572700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5637700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>850200</v>
+      </c>
+      <c r="E52" s="3">
         <v>966500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1503200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>655700</v>
       </c>
-      <c r="G52" s="3">
-        <v>559300</v>
-      </c>
       <c r="H52" s="3">
+        <v>1669200</v>
+      </c>
+      <c r="I52" s="3">
         <v>491200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>398700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>326400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1097000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>416500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>347800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>326700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>260900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>203400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>966900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>719800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>170800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>351900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>294600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20565600</v>
+      </c>
+      <c r="E54" s="3">
         <v>20777900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21161100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21512700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21544800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21901600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13316600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12619700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12503800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11915900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11736600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11359400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11434500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10730900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10304100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9607700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9292300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10003600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9885300</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,416 +3792,435 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>491900</v>
+      </c>
+      <c r="E57" s="3">
         <v>541400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>531300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>608900</v>
       </c>
-      <c r="G57" s="3">
-        <v>587600</v>
-      </c>
       <c r="H57" s="3">
+        <v>462400</v>
+      </c>
+      <c r="I57" s="3">
         <v>590100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>673700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>615200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>540100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>527400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>558900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>556200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>522100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>497200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>509500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>451700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>460500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2329500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2391500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2395200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>123000</v>
       </c>
-      <c r="G58" s="3">
-        <v>143300</v>
-      </c>
       <c r="H58" s="3">
+        <v>132800</v>
+      </c>
+      <c r="I58" s="3">
         <v>142700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>169300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>157400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>88300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>89000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>87100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>82600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>82000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>75900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>94800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>103200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>115400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>107700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>93300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1540900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1575700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1938500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1357600</v>
       </c>
-      <c r="G59" s="3">
-        <v>1355400</v>
-      </c>
       <c r="H59" s="3">
+        <v>1514100</v>
+      </c>
+      <c r="I59" s="3">
         <v>1476800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1283700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1233800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1725600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1719600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1581600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1388700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2064600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2075100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1548500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1317100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1188200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1466000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1280400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4997400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5271100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5509400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2927800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2796900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2922800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2633400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2543000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2414500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2348800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2268700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1998800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2705400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2707100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2165500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1917500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1813100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2025400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1834200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4025500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3283200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3135000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5365300</v>
       </c>
-      <c r="G61" s="3">
-        <v>5502300</v>
-      </c>
       <c r="H61" s="3">
+        <v>5248500</v>
+      </c>
+      <c r="I61" s="3">
         <v>5517500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5316200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5377100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5080200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5338400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5596700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5621400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5631700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5032500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5255700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5768300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4929900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4491600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4525200</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1027500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1237000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1187700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1234700</v>
       </c>
-      <c r="G62" s="3">
-        <v>971000</v>
-      </c>
       <c r="H62" s="3">
+        <v>1311100</v>
+      </c>
+      <c r="I62" s="3">
         <v>1002600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1149300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1181500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1702500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>805200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>745900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>772700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>766000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>736500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>753500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>747600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>681200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>718500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>660200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10478700</v>
+      </c>
+      <c r="E66" s="3">
         <v>10289000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10328300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10099100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9822300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10031900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9219400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9222700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10623000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9925400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9835800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9689000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10187500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9523100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9165400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9312100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8335300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8613000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8385600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-973100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-788500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-505400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-272500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-117100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-52200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>195000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-208200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-216200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10000</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
       <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
         <v>22900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-296600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-277100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-319600</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4703,14 +4876,17 @@
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4014200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4224800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4425700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4662100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4784700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4763100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2504300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2024800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1880800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1990500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1900800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1670300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1247000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1207700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1138700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>295600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>957000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1390600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1499800</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-165900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-264700</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
         <v>-137300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-69200</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>8000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-206200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>319500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>42500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-319600</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-553800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-57900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-134700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>316500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-294000</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E83" s="3">
         <v>73100</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3">
         <v>25600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>71600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>63600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>65600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>66000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>74800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>69200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>280700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>78500</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-36900</v>
+      </c>
+      <c r="E89" s="3">
         <v>157500</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3">
         <v>-136300</v>
       </c>
-      <c r="G89" s="3">
-        <v>105800</v>
-      </c>
       <c r="H89" s="3">
+        <v>94200</v>
+      </c>
+      <c r="I89" s="3">
         <v>85500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>96700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>96400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>189300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>271200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>176300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>250800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-51400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-70800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>392900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>315800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-59000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54400</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3">
         <v>-62800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-72800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-60800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-44200</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-55100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-53200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-58800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-135400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-31100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-38900</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-54500</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3">
         <v>-72200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-72900</v>
-      </c>
       <c r="H94" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-49100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-74100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-784200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-421600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>544700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-250500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-380200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>7600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>46100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>153300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-42500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6027,14 +6260,14 @@
       <c r="E96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F96" s="3">
-        <v>18100</v>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G96" s="3">
         <v>18100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
+      <c r="H96" s="3">
+        <v>18100</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>5</v>
@@ -6042,12 +6275,12 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>-10100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -6055,37 +6288,40 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-5200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-121000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-12100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-37000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>284600</v>
+      </c>
+      <c r="E100" s="3">
         <v>118100</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3">
         <v>-131500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-244300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-326000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>-89900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-281700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-275400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>26300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>589100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>475300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-77800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-428100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-51400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-145100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6600</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3">
         <v>3500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-13700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-16600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>9800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-16600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E102" s="3">
         <v>228300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-344000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-203400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-296100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-63800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-219000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-883900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-140700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>496600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>514300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>184600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-142200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>416100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-245300</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
